--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_WR.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_WR.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rc84ca99be5134aff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R277cd65e5bfa4297"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R66c46f11b9e74c11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rb5cdad6be2514f01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rb0ea77d401664a0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Re8551aa4b8b9436c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R1a8e63d163254f98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Rb44d62acd6fb4264"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Rcf11edfc565244af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Rc206ff32aff04411"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R0e655ea487e14249"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Rc24de9f301574d51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Rfead05532f2145f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Rea5d4ade09544e2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R9d765e2ac45a4304"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rc1698d9315b54814"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rda7f89bf1c5241e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R566b053c9f1a4ffd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R205e2f0089cd4740"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rd6b70996e538479d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R62f7a6edc3e647a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R0def5b7618b14725"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R7b9b245531154ac7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R44060ebec8014178"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R980505b25cb94c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rb5a94b961363418b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Rbf366a6ef2174928"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Rff0dfe6b69e64c17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Rdc053c1867ac4265"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Re2d82d55b5024c97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R2732009391384e79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Re95598dee4a449fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Rc7e0523406964451"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R606ab2ee52044b90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Rffdc13a07a1a4a26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rae97e7b89f7c4fb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R6baf48e246e4407e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Ra08549ad0ed242f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Rfd4d6008809f4f4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rdfb2ab063c12458c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R579d1762e36e49a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R1dddb7b0d68c4a2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R412770f5324244b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3964,6 +3965,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>エリック・アイゼンヘルツ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>昔のダンデリオン</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="13.5"/>

--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_WR.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_WR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cloude cowork\スキル秘伝HP\skill-sigil-web\資料\説明(パッシブ・スキル)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09458DC-5D0D-43E9-A350-3B9C96465E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4B7933-22B8-4EBC-965F-C80A2A3096F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26520" yWindow="1140" windowWidth="20115" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スキル(黒精霊の怒り)" sheetId="21" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="529">
   <si>
     <t>韓国語</t>
   </si>
@@ -401,9 +401,6 @@
   </si>
   <si>
     <t>PvE PvP ｜line flawless sharpness sharpness</t>
-  </si>
-  <si>
-    <t>PvE PvP ｜系列 無欠 鮮明 鮮明</t>
   </si>
   <si>
     <t>전방의 적에게 온 힘을 모아 크게 내려친다.</t>
@@ -1459,6 +1456,196 @@
   </si>
   <si>
     <t>　戦闘資源が最大の時、すべて消費してベルセルクの血発動（最大HPが10000以上の時のみ発動）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>PvE PvP</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>前方の敵に全力で打ち下ろす。</t>
+  </si>
+  <si>
+    <t>最大使用回数：2</t>
+  </si>
+  <si>
+    <t>再使用待機時間：5秒</t>
+  </si>
+  <si>
+    <t>・スキルボタン長押しで最大2打撃</t>
+  </si>
+  <si>
+    <t>・スキル使用中、スーパーアーマー</t>
+  </si>
+  <si>
+    <t>前方に向けて剣を二度強く振り、遮るすべてのものを斬り裂く。</t>
+  </si>
+  <si>
+    <t>最大使用回数：1</t>
+  </si>
+  <si>
+    <t>再使用待機時間：19秒</t>
+  </si>
+  <si>
+    <t>大剣を大きく3回振り回して前方の敵をうち壊す。</t>
+  </si>
+  <si>
+    <t>・スキル使用中、スーパーアーマー、キャッチ不可</t>
+  </si>
+  <si>
+    <t>ラバム技術 PvE PvP</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>全力を剣に集中して地面を裂いた後、前方に強く突き刺して敵を一掃する。</t>
+  </si>
+  <si>
+    <t>再使用待機時間：20秒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラバム技術 PvE PvP </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ジャンプ中、さらに高く飛び足元の敵を強く押しながらダメージを与える。</t>
+  </si>
+  <si>
+    <t>・ジャンプ中、ダメージ減少、キャッチ不可</t>
+  </si>
+  <si>
+    <t>大剣を前方へ大きく突き、敵に強力なダメージを与える。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PvP </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>素早く2回斬り上げながら剣気を飛ばす。</t>
+  </si>
+  <si>
+    <t>再使用待機時間：6秒</t>
+  </si>
+  <si>
+    <t>・スキル使用中、前方ガード</t>
+  </si>
+  <si>
+    <t>前方へ素早く移動しながら肩で敵を強打する。</t>
+  </si>
+  <si>
+    <t>再使用待機時間：2秒</t>
+  </si>
+  <si>
+    <t>・即時発動スキル</t>
+  </si>
+  <si>
+    <t>PvE</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>地面を強く叩いて、前方の敵を攻撃する。</t>
+  </si>
+  <si>
+    <t>再使用待機時間：10秒</t>
+  </si>
+  <si>
+    <t>・ジャンプ中、スーパーアーマー、ダメージ減少、キャッチ不可</t>
+  </si>
+  <si>
+    <t>・スキル使用時、不安定な大地発動</t>
+  </si>
+  <si>
+    <t>・不安定な大地</t>
+  </si>
+  <si>
+    <t>領域内の敵、4秒間移動速度20%減少,最大7打撃</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>空中にジャンプし周囲の敵を斬った後、地面を強く叩き下ろして周囲の敵に強力なダメージを与える。</t>
+  </si>
+  <si>
+    <t>・打撃成功時、浮かす</t>
+  </si>
+  <si>
+    <t>シールドで防ぐ状態を維持しながら瞬間的に敵にぶつかる。</t>
+  </si>
+  <si>
+    <t>・1回目の打撃成功時、硬直</t>
+  </si>
+  <si>
+    <t>前方の敵を大剣の面で殴る。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PvE </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵を持ち上げて肩越しに力一杯投げ下ろす。</t>
+  </si>
+  <si>
+    <t>・スキルボタン長押しで追加攻撃</t>
+  </si>
+  <si>
+    <t>・スキルボタン長押しで最大4打撃</t>
+  </si>
+  <si>
+    <t>・キャッチ試行中、スーパーアーマー、キャッチ不可</t>
+  </si>
+  <si>
+    <t>・キャッチ成功時、無敵</t>
+  </si>
+  <si>
+    <t>・キャッチ成功時、バウンド</t>
+  </si>
+  <si>
+    <t>すべての力を大剣に溜めて周りの敵をなぎ倒す。</t>
+  </si>
+  <si>
+    <t>再使用待機時間：7秒</t>
+  </si>
+  <si>
+    <t>・力を溜めている時、キャッチ不可</t>
+  </si>
+  <si>
+    <t>・力を1回溜めると、スキルダメージの125%適用</t>
+  </si>
+  <si>
+    <t>・力を2回溜めると、スキルダメージの200%適用</t>
+  </si>
+  <si>
+    <t>・敵と衝突しない</t>
+  </si>
+  <si>
+    <t>闇の精霊の力を借りて、黒いオーラの槍で攻撃する。</t>
+  </si>
+  <si>
+    <t>狂気を帯びた闘志で敵に突進する。</t>
+  </si>
+  <si>
+    <t>極限の怒りを引き出して、肉体を強化しHPを回復する。</t>
+  </si>
+  <si>
+    <t>・30秒間、クリティカルダメージ量＋50%</t>
+  </si>
+  <si>
+    <t>・30秒間、闇の精霊スキルダメージ量＋20%</t>
+  </si>
+  <si>
+    <t>・スキル使用時30秒間、回避スキルの再使用待機時間2秒減少</t>
+  </si>
+  <si>
+    <t>再使用待機時間：90秒</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・10秒間、2秒ごとにHP回復</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>・30秒間、攻撃力・防御力上昇</t>
+    <rPh sb="10" eb="15">
+      <t>ボウギョリョクジョウショウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1518,7 +1705,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1530,6 +1717,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1966,16 +2154,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>230</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1983,100 +2171,100 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="B4" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>236</v>
+      <c r="E4" s="5" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>167</v>
+      <c r="E5" s="5" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>127</v>
+      <c r="E6" s="5" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>173</v>
+      <c r="E7" s="5" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>133</v>
+      <c r="E8" s="5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>239</v>
+      <c r="E9" s="5" t="s">
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -2114,16 +2302,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2131,170 +2319,161 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>245</v>
+      <c r="E3" s="4" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>248</v>
+      <c r="E4" s="5" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>167</v>
+      <c r="E5" s="5" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>251</v>
+      <c r="E6" s="5" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>197</v>
+      <c r="E8" s="5" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>133</v>
+      <c r="E9" s="5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>255</v>
+      <c r="E10" s="5" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>258</v>
+      <c r="E11" s="5" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="B13" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -2332,16 +2511,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2349,35 +2528,35 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>273</v>
+      <c r="E3" s="4" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="B4" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>276</v>
+      <c r="E4" s="5" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>110</v>
@@ -2385,78 +2564,78 @@
       <c r="D5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
+      <c r="E5" s="5" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>127</v>
+      <c r="E6" s="5" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>173</v>
+      <c r="E7" s="5" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>212</v>
+      <c r="E8" s="5" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>279</v>
+      <c r="E9" s="5" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>215</v>
+      <c r="E10" s="5" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -2494,16 +2673,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2511,35 +2690,35 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>285</v>
+      <c r="E3" s="4" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>288</v>
+      <c r="E4" s="5" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>110</v>
@@ -2547,106 +2726,106 @@
       <c r="D5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
+      <c r="E5" s="5" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>291</v>
+      <c r="E6" s="5" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>294</v>
+      <c r="E7" s="5" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>297</v>
+      <c r="E8" s="5" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>300</v>
+      <c r="E9" s="5" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>303</v>
+      <c r="E10" s="5" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>306</v>
+      <c r="E11" s="5" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>309</v>
+      <c r="E12" s="5" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -2684,16 +2863,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>312</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2701,35 +2880,35 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>315</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="B4" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>318</v>
+      <c r="E4" s="5" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>110</v>
@@ -2737,22 +2916,22 @@
       <c r="D5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
+      <c r="E5" s="5" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>321</v>
+      <c r="E6" s="5" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2765,36 +2944,36 @@
       <c r="D7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>133</v>
+      <c r="E8" s="5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>324</v>
+      <c r="E9" s="5" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2807,64 +2986,61 @@
       <c r="D10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>327</v>
+      <c r="E11" s="5" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="27">
       <c r="B12" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>330</v>
+      <c r="E12" s="5" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="27">
       <c r="B13" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>333</v>
+      <c r="E13" s="5" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27">
       <c r="B14" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>335</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -2902,16 +3078,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>339</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2919,35 +3095,35 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>342</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="B4" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>345</v>
+      <c r="E4" s="5" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>110</v>
@@ -2955,36 +3131,36 @@
       <c r="D5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
+      <c r="E5" s="5" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>321</v>
+      <c r="E6" s="5" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>133</v>
+      <c r="E7" s="5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2997,22 +3173,22 @@
       <c r="D8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>348</v>
+      <c r="E9" s="5" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -3050,16 +3226,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>351</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3067,35 +3243,35 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>354</v>
+      <c r="E3" s="4" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>357</v>
+      <c r="E4" s="5" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>110</v>
@@ -3103,64 +3279,64 @@
       <c r="D5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
+      <c r="E5" s="5" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>321</v>
+      <c r="E6" s="5" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>360</v>
+      <c r="E7" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>133</v>
+      <c r="E8" s="5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>363</v>
+      <c r="E9" s="5" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -3198,16 +3374,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>366</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="27">
@@ -3215,21 +3391,21 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>369</v>
+      <c r="E3" s="5" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>110</v>
@@ -3237,106 +3413,103 @@
       <c r="D4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>111</v>
+      <c r="E4" s="5" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>372</v>
+      <c r="E5" s="5" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>374</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>378</v>
+      <c r="E7" s="5" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>381</v>
+      <c r="E8" s="5" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>384</v>
+      <c r="E9" s="5" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>387</v>
+      <c r="E10" s="5" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="27">
       <c r="B11" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>390</v>
+      <c r="E11" s="5" t="s">
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -3374,16 +3547,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>393</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3391,35 +3564,35 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>396</v>
+      <c r="E3" s="4" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="B4" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>399</v>
+      <c r="E4" s="5" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>110</v>
@@ -3427,50 +3600,50 @@
       <c r="D5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
+      <c r="E5" s="5" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>402</v>
+      <c r="E6" s="5" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>173</v>
+      <c r="E7" s="5" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>133</v>
+      <c r="E8" s="5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3483,7 +3656,7 @@
       <c r="D9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="5" t="s">
         <v>24</v>
       </c>
     </row>
@@ -3522,16 +3695,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>405</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3539,35 +3712,35 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>396</v>
+      <c r="E3" s="4" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="B4" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>408</v>
+      <c r="E4" s="5" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>110</v>
@@ -3575,64 +3748,64 @@
       <c r="D5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
+      <c r="E5" s="5" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>402</v>
+      <c r="E6" s="5" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>411</v>
+      <c r="E7" s="5" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>414</v>
+      <c r="E8" s="5" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>136</v>
+      <c r="E9" s="5" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -3697,7 +3870,7 @@
         <v>40</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3711,7 +3884,7 @@
         <v>43</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="27">
@@ -3725,7 +3898,7 @@
         <v>46</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3739,7 +3912,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="27">
@@ -3753,7 +3926,7 @@
         <v>52</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27">
@@ -3767,7 +3940,7 @@
         <v>55</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3781,7 +3954,7 @@
         <v>58</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="27">
@@ -3795,7 +3968,7 @@
         <v>61</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="27">
@@ -3837,7 +4010,7 @@
         <v>70</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -3875,16 +4048,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>417</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3892,35 +4065,35 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>420</v>
+      <c r="E3" s="4" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="B4" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>423</v>
+      <c r="E4" s="5" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>110</v>
@@ -3928,64 +4101,64 @@
       <c r="D5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
+      <c r="E5" s="5" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>291</v>
+      <c r="E6" s="5" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>130</v>
+      <c r="E7" s="5" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>133</v>
+      <c r="E8" s="5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>179</v>
+      <c r="E9" s="5" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -4023,16 +4196,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>426</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4040,35 +4213,35 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>420</v>
+      <c r="E3" s="4" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="B4" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>429</v>
+      <c r="E4" s="5" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>110</v>
@@ -4076,64 +4249,64 @@
       <c r="D5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
+      <c r="E5" s="5" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>402</v>
+      <c r="E6" s="5" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>173</v>
+      <c r="E7" s="5" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>133</v>
+      <c r="E8" s="5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>432</v>
+      <c r="E9" s="5" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4146,7 +4319,7 @@
       <c r="D10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="5" t="s">
         <v>24</v>
       </c>
     </row>
@@ -4167,23 +4340,23 @@
   <sheetData>
     <row r="1" spans="1:2" ht="19.5" customHeight="1">
       <c r="A1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B1" t="s">
         <v>463</v>
-      </c>
-      <c r="B1" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="19.5" customHeight="1">
       <c r="A2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B2" t="s">
         <v>465</v>
-      </c>
-      <c r="B2" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="19.5" customHeight="1">
       <c r="A3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -4247,7 +4420,7 @@
         <v>76</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="40.5">
@@ -4261,7 +4434,7 @@
         <v>79</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4275,7 +4448,7 @@
         <v>82</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="27">
@@ -4289,7 +4462,7 @@
         <v>85</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4303,7 +4476,7 @@
         <v>88</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27">
@@ -4317,7 +4490,7 @@
         <v>91</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="27">
@@ -4331,7 +4504,7 @@
         <v>94</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4345,7 +4518,7 @@
         <v>97</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="54">
@@ -4359,7 +4532,7 @@
         <v>100</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="27">
@@ -4373,7 +4546,7 @@
         <v>103</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -4523,30 +4696,30 @@
       <c r="C3" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>120</v>
+      <c r="D3" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>123</v>
+      <c r="E4" s="5" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>110</v>
@@ -4554,64 +4727,64 @@
       <c r="D5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
+      <c r="E5" s="5" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>127</v>
+      <c r="E6" s="5" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>130</v>
+      <c r="E7" s="5" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>133</v>
+      <c r="E8" s="5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>136</v>
+      <c r="E9" s="5" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4619,70 +4792,59 @@
         <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="B13" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>136</v>
-      </c>
+      <c r="E14" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -4719,16 +4881,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4736,35 +4898,35 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>149</v>
+      <c r="E3" s="4" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>152</v>
+      <c r="E4" s="5" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>110</v>
@@ -4772,64 +4934,64 @@
       <c r="D5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
+      <c r="E5" s="5" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>127</v>
+      <c r="E6" s="5" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>130</v>
+      <c r="E7" s="5" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>133</v>
+      <c r="E8" s="5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>155</v>
+      <c r="E9" s="5" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -4867,16 +5029,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4884,128 +5046,122 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>164</v>
+      <c r="E4" s="5" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>167</v>
+      <c r="E5" s="5" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>170</v>
+      <c r="E6" s="5" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>173</v>
+      <c r="E7" s="5" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>176</v>
+      <c r="E8" s="5" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>179</v>
+      <c r="E9" s="5" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -5043,16 +5199,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5060,35 +5216,35 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>191</v>
+      <c r="E3" s="4" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="27">
       <c r="B4" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>194</v>
+      <c r="E4" s="5" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>110</v>
@@ -5096,78 +5252,78 @@
       <c r="D5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>111</v>
+      <c r="E5" s="5" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>127</v>
+      <c r="E6" s="5" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>130</v>
+      <c r="E7" s="5" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>197</v>
+      <c r="E8" s="5" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>133</v>
+      <c r="E9" s="5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>179</v>
+      <c r="E10" s="5" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -5178,7 +5334,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -5205,16 +5361,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5222,171 +5378,172 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>206</v>
+      <c r="E4" s="5" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="B5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>167</v>
+      <c r="E5" s="5" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>209</v>
+      <c r="E6" s="5" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>130</v>
+      <c r="E7" s="5" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="B8" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>212</v>
+      <c r="E8" s="5" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>133</v>
+      <c r="E9" s="5" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>215</v>
+      <c r="E10" s="5" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="B11" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>218</v>
+      <c r="E11" s="5" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>221</v>
+      <c r="E12" s="5" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="27">
       <c r="B13" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>224</v>
+      <c r="E13" s="4" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="B14" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>227</v>
-      </c>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
